--- a/doc/Микросхемы_цены.xlsx
+++ b/doc/Микросхемы_цены.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Prog\GitHub\Sasha7b9\HomePC\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE3C9D64-562B-4B87-BAE7-69A5A96C5B2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E83C439-A3AD-43BF-9107-02FBE6767114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16455" yWindow="4500" windowWidth="19170" windowHeight="15330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10020" yWindow="5550" windowWidth="19170" windowHeight="15330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
   <si>
     <t>К155ТМ2</t>
   </si>
@@ -262,6 +262,9 @@
   </si>
   <si>
     <t>К573РФ3</t>
+  </si>
+  <si>
+    <t>К155ИР13</t>
   </si>
 </sst>
 </file>
@@ -269,7 +272,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="#,##0.00\ _₽"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00\ _₽"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -344,8 +347,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -673,7 +676,9 @@
         <v>2</v>
       </c>
       <c r="C3"/>
-      <c r="D3"/>
+      <c r="D3">
+        <v>4.96</v>
+      </c>
       <c r="E3"/>
       <c r="F3"/>
       <c r="G3" s="11"/>
@@ -687,7 +692,9 @@
         <v>6</v>
       </c>
       <c r="C4"/>
-      <c r="D4"/>
+      <c r="D4">
+        <v>1.26</v>
+      </c>
       <c r="E4"/>
       <c r="F4"/>
       <c r="G4" s="11"/>
@@ -701,7 +708,9 @@
         <v>3</v>
       </c>
       <c r="C5"/>
-      <c r="D5"/>
+      <c r="D5">
+        <v>2.92</v>
+      </c>
       <c r="E5"/>
       <c r="F5"/>
       <c r="G5" s="11"/>
@@ -715,7 +724,9 @@
         <v>3</v>
       </c>
       <c r="C6"/>
-      <c r="D6"/>
+      <c r="D6">
+        <v>1.38</v>
+      </c>
       <c r="E6"/>
       <c r="F6"/>
       <c r="G6" s="11"/>
@@ -729,7 +740,9 @@
         <v>18</v>
       </c>
       <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
+      <c r="D7" s="13">
+        <v>1.17</v>
+      </c>
       <c r="E7" s="12"/>
       <c r="F7"/>
       <c r="G7" s="11"/>
@@ -739,9 +752,13 @@
       <c r="A8" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="8"/>
+      <c r="B8" s="8">
+        <v>3</v>
+      </c>
       <c r="C8"/>
-      <c r="D8"/>
+      <c r="D8">
+        <v>1.17</v>
+      </c>
       <c r="E8"/>
       <c r="F8"/>
       <c r="G8" s="11"/>
@@ -751,9 +768,13 @@
       <c r="A9" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="8"/>
+      <c r="B9" s="8">
+        <v>2</v>
+      </c>
       <c r="C9"/>
-      <c r="D9"/>
+      <c r="D9">
+        <v>2.93</v>
+      </c>
       <c r="E9"/>
       <c r="F9"/>
       <c r="G9" s="11"/>
@@ -767,7 +788,9 @@
         <v>6</v>
       </c>
       <c r="C10"/>
-      <c r="D10"/>
+      <c r="D10">
+        <v>1.61</v>
+      </c>
       <c r="E10"/>
       <c r="F10"/>
       <c r="G10" s="11"/>
@@ -775,9 +798,11 @@
     </row>
     <row r="11" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B11" s="8"/>
+        <v>79</v>
+      </c>
+      <c r="B11" s="8">
+        <v>3</v>
+      </c>
       <c r="C11"/>
       <c r="D11"/>
       <c r="E11"/>
@@ -793,7 +818,9 @@
         <v>9</v>
       </c>
       <c r="C12"/>
-      <c r="D12"/>
+      <c r="D12">
+        <v>1.49</v>
+      </c>
       <c r="E12"/>
       <c r="F12"/>
       <c r="G12" s="11"/>
@@ -807,7 +834,9 @@
         <v>5</v>
       </c>
       <c r="C13"/>
-      <c r="D13"/>
+      <c r="D13">
+        <v>0.28999999999999998</v>
+      </c>
       <c r="E13"/>
       <c r="F13"/>
       <c r="G13" s="11"/>
@@ -821,7 +850,9 @@
         <v>7</v>
       </c>
       <c r="C14"/>
-      <c r="D14"/>
+      <c r="D14">
+        <v>0.53</v>
+      </c>
       <c r="E14"/>
       <c r="F14"/>
       <c r="G14" s="11"/>
@@ -835,7 +866,9 @@
         <v>16</v>
       </c>
       <c r="C15"/>
-      <c r="D15"/>
+      <c r="D15">
+        <v>0.47</v>
+      </c>
       <c r="E15"/>
       <c r="F15"/>
       <c r="G15" s="11"/>
@@ -845,9 +878,13 @@
       <c r="A16" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="8"/>
+      <c r="B16" s="8">
+        <v>3</v>
+      </c>
       <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
+      <c r="D16" s="8">
+        <v>0.47</v>
+      </c>
       <c r="E16"/>
       <c r="F16"/>
       <c r="G16" s="11"/>
@@ -857,9 +894,13 @@
       <c r="A17" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B17" s="8"/>
+      <c r="B17" s="8">
+        <v>2</v>
+      </c>
       <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
+      <c r="D17" s="8">
+        <v>0.28999999999999998</v>
+      </c>
       <c r="E17"/>
       <c r="F17"/>
       <c r="G17" s="11"/>
@@ -873,7 +914,9 @@
         <v>5</v>
       </c>
       <c r="C18" s="8"/>
-      <c r="D18"/>
+      <c r="D18" s="8">
+        <v>0.28999999999999998</v>
+      </c>
       <c r="E18"/>
       <c r="F18"/>
       <c r="G18" s="11"/>
@@ -883,9 +926,13 @@
       <c r="A19" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B19" s="8"/>
+      <c r="B19" s="8">
+        <v>4</v>
+      </c>
       <c r="C19"/>
-      <c r="D19"/>
+      <c r="D19" s="8">
+        <v>1.81</v>
+      </c>
       <c r="E19"/>
       <c r="F19"/>
       <c r="G19" s="11"/>
@@ -895,13 +942,17 @@
       <c r="A20" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="8"/>
+      <c r="B20" s="8">
+        <v>2</v>
+      </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B21" s="8"/>
+      <c r="B21" s="8">
+        <v>4</v>
+      </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
@@ -915,7 +966,9 @@
       <c r="A23" t="s">
         <v>61</v>
       </c>
-      <c r="B23" s="8"/>
+      <c r="B23" s="8">
+        <v>3</v>
+      </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
@@ -924,24 +977,33 @@
       <c r="B24" s="8">
         <v>8</v>
       </c>
+      <c r="D24">
+        <v>0.23</v>
+      </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>63</v>
       </c>
-      <c r="B25" s="8"/>
+      <c r="B25" s="8">
+        <v>3</v>
+      </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="8"/>
+      <c r="B26" s="8">
+        <v>2</v>
+      </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>3</v>
       </c>
-      <c r="B27" s="8"/>
+      <c r="B27" s="8">
+        <v>3</v>
+      </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
@@ -950,19 +1012,26 @@
       <c r="B28" s="8">
         <v>7</v>
       </c>
+      <c r="D28">
+        <v>1.17</v>
+      </c>
       <c r="E28" s="7"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>64</v>
       </c>
-      <c r="B29" s="8"/>
+      <c r="B29" s="8">
+        <v>2</v>
+      </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="8"/>
+      <c r="B30" s="8">
+        <v>2</v>
+      </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
@@ -979,8 +1048,11 @@
       <c r="B32" s="8">
         <v>6</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D32">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -988,7 +1060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>39</v>
       </c>
@@ -996,7 +1068,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>67</v>
       </c>
@@ -1004,7 +1076,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>68</v>
       </c>
@@ -1012,7 +1084,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>11</v>
       </c>
@@ -1020,7 +1092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>43</v>
       </c>
@@ -1028,7 +1100,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>12</v>
       </c>
@@ -1036,7 +1108,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>69</v>
       </c>
@@ -1044,7 +1116,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>70</v>
       </c>
@@ -1052,23 +1124,29 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>17</v>
       </c>
       <c r="B42" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D42">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>71</v>
       </c>
       <c r="B43" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D43">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>72</v>
       </c>
@@ -1076,30 +1154,42 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>44</v>
       </c>
       <c r="B45">
         <v>13</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D45">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>73</v>
       </c>
       <c r="B46">
         <v>6</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D46">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B47">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>32</v>
+      </c>
+      <c r="B48">
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
